--- a/01-Translation/04_translate_experiment/task_translation_template.xlsx
+++ b/01-Translation/04_translate_experiment/task_translation_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erinbuchanan/GitHub/Research/2_projects/ManyLanguages-Grant/ML-One-Network/01-Translation/04_translate_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CC8204-00F7-D548-805A-A416E0736598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAB953E-A726-6447-A22A-21C96EC27417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>English</t>
   </si>
@@ -139,9 +139,6 @@
     <t>For each word, enter the age (in years) when you think you learned it. An approximate age is good enough for this rating. If you do not know the word, please select the letter X for unknown.</t>
   </si>
   <si>
-    <t>Great job! Remember you should use the ${ window.word_key } key for real word, and the ${ window.nonword_key } for fake word.</t>
-  </si>
-  <si>
     <t>High school diploma</t>
   </si>
   <si>
@@ -157,9 +154,6 @@
     <t>If you do not know the word, please select the letter X for unknown.</t>
   </si>
   <si>
-    <t>If you recognize the word on the screen like COLD , please press the ${ window.word_key } key for real word. If the word is made-up nonsense, like WERM , please press ${ window.nonword_key } for fake word. During practice, we will give you feedback.</t>
-  </si>
-  <si>
     <t>Imageability Study</t>
   </si>
   <si>
@@ -223,18 +217,6 @@
     <t>Please press ${ window.word_key } if the above is a real word, and ${ window.nonword_key } if it is a fake word.</t>
   </si>
   <si>
-    <t>Please press Space to consent to the study and continue.</t>
-  </si>
-  <si>
-    <t>Please press the Space Bar to continue or wait until this page disappears.</t>
-  </si>
-  <si>
-    <t>Please press the Space Bar to continue.</t>
-  </si>
-  <si>
-    <t>Please press the Space Bar to try a few for practice.</t>
-  </si>
-  <si>
     <t>Please rate the following words by entering the age in years at which you think you learned the word. An approximate age is good enough for this rating.</t>
   </si>
   <si>
@@ -280,9 +262,6 @@
     <t>Rating (1 = very unpleasant/unhappy, 9 = very pleasant/happy) or X (Don't know the word)</t>
   </si>
   <si>
-    <t>Remember you should use the ${ window.word_key } key for real word, and the ${ window.nonword_key } for fake word.</t>
-  </si>
-  <si>
     <t>Right-handed</t>
   </si>
   <si>
@@ -391,7 +370,31 @@
     <t>Your participant number is:</t>
   </si>
   <si>
-    <t>Your random participant id is: ${ window.uuid }. You can use this number to give to your experimenter to show you completed the experiment.</t>
+    <t>If you recognize the word on the screen like &lt;b&gt;COLD&lt;/b&gt;, please press the &lt;kbd&gt;${ window.word_key }&lt;/kbd&gt; key for real word. If the word is made-up nonsense, like &lt;b&gt;WERM&lt;/b&gt;, please press &lt;kbd&gt;${ window.nonword_key }&lt;/kbd&gt; for fake word. During practice, we will give you feedback.</t>
+  </si>
+  <si>
+    <t>Please press the &lt;kbd&gt;Space Bar&lt;/kbd&gt; to try a few for practice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your random participant id is: </t>
+  </si>
+  <si>
+    <t>Great job! Remember you should use the &lt;kbd&gt;${ window.word_key }&lt;/kbd&gt; key for real word, and the &lt;kbd&gt;${ window.nonword_key } &lt;/kbd&gt; for fake word.</t>
+  </si>
+  <si>
+    <t>Please press the &lt;kbd&gt;Space Bar&lt;/kbd&gt; to continue.</t>
+  </si>
+  <si>
+    <t>Remember you should use the &lt;kbd&gt;${ window.word_key }&lt;/kbd&gt; key for real word, and the &lt;kbd&gt;${ window.nonword_key } &lt;/kbd&gt; for fake word.</t>
+  </si>
+  <si>
+    <t>Please press the &lt;kbd&gt;Space Bar&lt;/kbd&gt; to continue or wait until this page disappears.</t>
+  </si>
+  <si>
+    <t>Please press &lt;kbd&gt;Space&lt;/kbd&gt; to consent to the study and continue.</t>
+  </si>
+  <si>
+    <t>You can use this number to give to your experimenter to show you completed the experiment.</t>
   </si>
 </sst>
 </file>
@@ -775,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A124"/>
+  <dimension ref="A1:A125"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="86.33203125" style="1" customWidth="1"/>
@@ -979,432 +982,440 @@
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>39</v>
+    <row r="40" spans="1:1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>45</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="85" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>86</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A87" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="153" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="95" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96" spans="1:1" ht="119" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="97" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="98" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="102" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="105" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="106" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="107" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="108" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:1" ht="136" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="110" spans="1:1" ht="34" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="112" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="113" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="114" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="115" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="116" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="117" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="120" spans="1:1" ht="68" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="122" spans="1:1" ht="51" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="123" spans="1:1" ht="17" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>123</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G133">
+    <sortCondition ref="A2:A133"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>

--- a/01-Translation/04_translate_experiment/task_translation_template.xlsx
+++ b/01-Translation/04_translate_experiment/task_translation_template.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erinbuchanan/GitHub/Research/2_projects/ManyLanguages-Grant/ML-One-Network/01-Translation/04_translate_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAB953E-A726-6447-A22A-21C96EC27417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8247F191-7344-6545-89F8-FD4D25F83D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="aoa" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -139,6 +139,9 @@
     <t>For each word, enter the age (in years) when you think you learned it. An approximate age is good enough for this rating. If you do not know the word, please select the letter X for unknown.</t>
   </si>
   <si>
+    <t>Great job! Remember you should use the &lt;kbd&gt;${ window.word_key }&lt;/kbd&gt; key for real word, and the &lt;kbd&gt;${ window.nonword_key } &lt;/kbd&gt; for fake word.</t>
+  </si>
+  <si>
     <t>High school diploma</t>
   </si>
   <si>
@@ -154,6 +157,9 @@
     <t>If you do not know the word, please select the letter X for unknown.</t>
   </si>
   <si>
+    <t>If you recognize the word on the screen like &lt;b&gt;COLD&lt;/b&gt;, please press the &lt;kbd&gt;${ window.word_key }&lt;/kbd&gt; key for real word. If the word is made-up nonsense, like &lt;b&gt;WERM&lt;/b&gt;, please press &lt;kbd&gt;${ window.nonword_key }&lt;/kbd&gt; for fake word. During practice, we will give you feedback.</t>
+  </si>
+  <si>
     <t>Imageability Study</t>
   </si>
   <si>
@@ -214,7 +220,16 @@
     <t>Please note that your data will be anonymous, which means you cannot ask for it to be removed once you have completed the study.</t>
   </si>
   <si>
-    <t>Please press ${ window.word_key } if the above is a real word, and ${ window.nonword_key } if it is a fake word.</t>
+    <t>Please press &lt;kbd&gt;Space&lt;/kbd&gt; to consent to the study and continue.</t>
+  </si>
+  <si>
+    <t>Please press the &lt;kbd&gt;Space Bar&lt;/kbd&gt; to continue or wait until this page disappears.</t>
+  </si>
+  <si>
+    <t>Please press the &lt;kbd&gt;Space Bar&lt;/kbd&gt; to continue.</t>
+  </si>
+  <si>
+    <t>Please press the &lt;kbd&gt;Space Bar&lt;/kbd&gt; to try a few for practice.</t>
   </si>
   <si>
     <t>Please rate the following words by entering the age in years at which you think you learned the word. An approximate age is good enough for this rating.</t>
@@ -262,6 +277,9 @@
     <t>Rating (1 = very unpleasant/unhappy, 9 = very pleasant/happy) or X (Don't know the word)</t>
   </si>
   <si>
+    <t>Remember you should use the &lt;kbd&gt;${ window.word_key }&lt;/kbd&gt; key for real word, and the &lt;kbd&gt;${ window.nonword_key } &lt;/kbd&gt; for fake word.</t>
+  </si>
+  <si>
     <t>Right-handed</t>
   </si>
   <si>
@@ -370,31 +388,13 @@
     <t>Your participant number is:</t>
   </si>
   <si>
-    <t>If you recognize the word on the screen like &lt;b&gt;COLD&lt;/b&gt;, please press the &lt;kbd&gt;${ window.word_key }&lt;/kbd&gt; key for real word. If the word is made-up nonsense, like &lt;b&gt;WERM&lt;/b&gt;, please press &lt;kbd&gt;${ window.nonword_key }&lt;/kbd&gt; for fake word. During practice, we will give you feedback.</t>
-  </si>
-  <si>
-    <t>Please press the &lt;kbd&gt;Space Bar&lt;/kbd&gt; to try a few for practice.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Your random participant id is: </t>
   </si>
   <si>
-    <t>Great job! Remember you should use the &lt;kbd&gt;${ window.word_key }&lt;/kbd&gt; key for real word, and the &lt;kbd&gt;${ window.nonword_key } &lt;/kbd&gt; for fake word.</t>
-  </si>
-  <si>
-    <t>Please press the &lt;kbd&gt;Space Bar&lt;/kbd&gt; to continue.</t>
-  </si>
-  <si>
-    <t>Remember you should use the &lt;kbd&gt;${ window.word_key }&lt;/kbd&gt; key for real word, and the &lt;kbd&gt;${ window.nonword_key } &lt;/kbd&gt; for fake word.</t>
-  </si>
-  <si>
-    <t>Please press the &lt;kbd&gt;Space Bar&lt;/kbd&gt; to continue or wait until this page disappears.</t>
-  </si>
-  <si>
-    <t>Please press &lt;kbd&gt;Space&lt;/kbd&gt; to consent to the study and continue.</t>
-  </si>
-  <si>
     <t>You can use this number to give to your experimenter to show you completed the experiment.</t>
+  </si>
+  <si>
+    <t>Please press &lt;kbd&gt;${ window.word_key }&lt;/kbd&gt; if the above is a real word, and &lt;kbd&gt;${ window.nonword_key }&lt;/kbd&gt; if it is a fake word.</t>
   </si>
 </sst>
 </file>
@@ -403,17 +403,16 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -424,7 +423,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -432,24 +431,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -472,44 +483,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -536,32 +547,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -588,24 +581,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -617,258 +592,256 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A125"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="86.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="76" style="1" customWidth="1"/>
-    <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="68" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="102" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="102" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
@@ -877,43 +850,43 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
     </row>
@@ -927,496 +900,495 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A57" s="1" t="s">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A58" s="1" t="s">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="85" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A60" s="1" t="s">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A63" s="1" t="s">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A66" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" s="1" t="s">
-        <v>123</v>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="80" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A80" s="1" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="81" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A84" s="1" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="85" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A85" s="1" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="86" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A86" s="1" t="s">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="87" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A87" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="89" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A89" s="1" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="90" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A90" s="1" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="91" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A91" s="1" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="153" x14ac:dyDescent="0.2">
-      <c r="A92" s="1" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A94" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A95" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" ht="119" x14ac:dyDescent="0.2">
-      <c r="A96" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A97" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A98" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A100" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A102" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A103" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A104" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A105" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A106" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A107" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="108" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A108" s="1" t="s">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="109" spans="1:1" ht="136" x14ac:dyDescent="0.2">
-      <c r="A109" s="1" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="110" spans="1:1" ht="34" x14ac:dyDescent="0.2">
-      <c r="A110" s="1" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
         <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A112" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A113" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A114" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A115" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A116" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A117" s="1" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" ht="68" x14ac:dyDescent="0.2">
-      <c r="A120" s="1" t="s">
-        <v>112</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A122" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A123" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A124" s="1" t="s">
         <v>118</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G133">
-    <sortCondition ref="A2:A133"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A126">
+    <sortCondition ref="A2:A126"/>
   </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>